--- a/data/Basketball_Analytics_2022-2023.xlsx
+++ b/data/Basketball_Analytics_2022-2023.xlsx
@@ -6882,8 +6882,14 @@
           <t>Israel</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>1991-07-05</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>1.93</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6896,7 +6902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E222"/>
+  <dimension ref="A1:E223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11048,6 +11054,25 @@
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>13030</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>21</v>
+      </c>
+      <c r="E223" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11582,61 +11607,61 @@
         <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>5294</v>
+        <v>5446</v>
       </c>
       <c r="D8" t="n">
-        <v>2282</v>
+        <v>2316</v>
       </c>
       <c r="E8" t="n">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="F8" t="n">
-        <v>1774</v>
+        <v>1808</v>
       </c>
       <c r="G8" t="n">
-        <v>46</v>
+        <v>45.8</v>
       </c>
       <c r="H8" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="I8" t="n">
-        <v>672</v>
+        <v>686</v>
       </c>
       <c r="J8" t="n">
         <v>31</v>
       </c>
       <c r="K8" t="n">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="L8" t="n">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="M8" t="n">
-        <v>72.2</v>
+        <v>72.3</v>
       </c>
       <c r="N8" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="O8" t="n">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="P8" t="n">
-        <v>870</v>
+        <v>879</v>
       </c>
       <c r="Q8" t="n">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="R8" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="S8" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="T8" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>2557</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="9">
@@ -32016,61 +32041,61 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="D7" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="G7" t="n">
-        <v>42.4</v>
+        <v>41.6</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J7" t="n">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L7" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M7" t="n">
-        <v>63</v>
+        <v>61.4</v>
       </c>
       <c r="N7" t="n">
         <v>26</v>
       </c>
       <c r="O7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P7" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8">
